--- a/08_tables/q8_between_full_correlation_matrix_with_trend_lags.xlsx
+++ b/08_tables/q8_between_full_correlation_matrix_with_trend_lags.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q8_between_full_correlation_matrix_with_trend_lags.xlsx
+++ b/08_tables/q8_between_full_correlation_matrix_with_trend_lags.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,134 +417,134 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>GDP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SHORTUN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>LONGUN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>LF</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>REER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>i_lag1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>P_lag1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>W_lag1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>WR_lag1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>GDP_lag1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LS_lag1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UN_lag1</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>SHORTUN_lag1</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>LONGUN_lag1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>LF_lag1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>REER_lag1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SH_lag1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>i</t>
         </is>
@@ -565,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8849645363512298</v>
+        <v>-0.8849645363512297</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5419273973247576</v>
@@ -574,7 +562,7 @@
         <v>0.8807257491182118</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.372100664392557</v>
+        <v>-0.3721006643925569</v>
       </c>
       <c r="G2" t="n">
         <v>-0.317899981085866</v>
@@ -583,23 +571,23 @@
         <v>0.3820778906126966</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.251050212271769</v>
+        <v>-0.2510502122717689</v>
       </c>
       <c r="J2" t="n">
         <v>-0.09848815227339781</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4227834725036978</v>
+        <v>-0.4227834725036979</v>
       </c>
       <c r="L2" t="n">
         <v>-0.6511442979749542</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9752949454945217</v>
+        <v>0.975294945494522</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0.9998992510323782</v>
+        <v>0.9998992510323784</v>
       </c>
       <c r="P2" t="n">
         <v>-0.8842654704070894</v>
@@ -614,10 +602,10 @@
         <v>-0.3732451966537225</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3115988637288141</v>
+        <v>-0.3115988637288138</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3780556684554928</v>
+        <v>0.3780556684554927</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2523627093172098</v>
@@ -632,91 +620,91 @@
         <v>-0.6488783302109221</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9812990370124334</v>
+        <v>0.9812990370124332</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.8849645363512298</v>
+        <v>-0.8849645363512297</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3804274980234754</v>
+        <v>0.3804274980234753</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8854837924636482</v>
+        <v>-0.8854837924636483</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1689118841219407</v>
+        <v>0.1689118841219411</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1695082015933334</v>
+        <v>0.1695082015933333</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5218178715827039</v>
+        <v>-0.5218178715827038</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008001483884778154</v>
+        <v>0.008001483884778634</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.01681270971069045</v>
+        <v>-0.01681270971069017</v>
       </c>
       <c r="K3" t="n">
-        <v>0.258471533393825</v>
+        <v>0.2584715333938255</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7188545818735906</v>
+        <v>0.7188545818735909</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8778495188046286</v>
+        <v>-0.8778495188046287</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>-0.8838733630051855</v>
       </c>
       <c r="P3" t="n">
-        <v>0.999979598161744</v>
+        <v>0.9999795981617441</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.391177043687978</v>
+        <v>0.3911770436879778</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.8857251257792353</v>
+        <v>-0.8857251257792357</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1707307134684574</v>
+        <v>0.1707307134684579</v>
       </c>
       <c r="T3" t="n">
-        <v>0.16488269473364</v>
+        <v>0.1648826947336396</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5211286847283035</v>
+        <v>-0.5211286847283034</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00927383905652389</v>
+        <v>0.009273839056524381</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0152591156095372</v>
+        <v>-0.01525911560953693</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2595819444228162</v>
+        <v>0.2595819444228167</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7218128932997563</v>
+        <v>0.7218128932997564</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.8858558550615289</v>
+        <v>-0.8858558550615293</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -725,25 +713,25 @@
         <v>-0.5419273973247576</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3804274980234754</v>
+        <v>0.3804274980234753</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3425592462896986</v>
+        <v>-0.3425592462896985</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4785779298235905</v>
+        <v>0.4785779298235904</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2123628771197048</v>
+        <v>0.2123628771197047</v>
       </c>
       <c r="H4" t="n">
         <v>-0.1369084253785725</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4325186825946399</v>
+        <v>0.43251868259464</v>
       </c>
       <c r="J4" t="n">
         <v>0.1897759717511375</v>
@@ -774,10 +762,10 @@
         <v>0.4786708181867887</v>
       </c>
       <c r="T4" t="n">
-        <v>0.20475216561385</v>
+        <v>0.2047521656138495</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1327089361697054</v>
+        <v>-0.1327089361697055</v>
       </c>
       <c r="V4" t="n">
         <v>0.4329105172837279</v>
@@ -792,11 +780,11 @@
         <v>0.3386512962748404</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.5090969913149572</v>
+        <v>-0.5090969913149573</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -805,44 +793,44 @@
         <v>0.8807257491182118</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.8854837924636482</v>
+        <v>-0.8854837924636483</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3425592462896986</v>
+        <v>-0.3425592462896985</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1899389656328979</v>
+        <v>-0.1899389656328978</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2047453459706184</v>
+        <v>-0.2047453459706183</v>
       </c>
       <c r="H5" t="n">
-        <v>0.368907005219515</v>
+        <v>0.3689070052195151</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09713944074218601</v>
+        <v>-0.097139440742186</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02672745349588758</v>
+        <v>0.0267274534958875</v>
       </c>
       <c r="K5" t="n">
         <v>-0.2546519718232717</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.617561074095845</v>
+        <v>-0.6175610740958448</v>
       </c>
       <c r="M5" t="n">
-        <v>0.861899747052612</v>
+        <v>0.8618997470526121</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>0.8808462549912839</v>
+        <v>0.8808462549912837</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8851276130955023</v>
+        <v>-0.885127613095502</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.3500082614971569</v>
@@ -851,19 +839,19 @@
         <v>0.9998600426704776</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1909683191999004</v>
+        <v>-0.1909683191999005</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1990443653837984</v>
+        <v>-0.1990443653837979</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3661557605034371</v>
+        <v>0.366155760503437</v>
       </c>
       <c r="V5" t="n">
         <v>-0.09823819873572447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02373977285307798</v>
+        <v>0.0237397728530779</v>
       </c>
       <c r="X5" t="n">
         <v>-0.255251532946594</v>
@@ -876,22 +864,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>GDP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.372100664392557</v>
+        <v>-0.3721006643925569</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1689118841219407</v>
+        <v>0.1689118841219411</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4785779298235905</v>
+        <v>0.4785779298235904</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1899389656328979</v>
+        <v>-0.1899389656328978</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -903,10 +891,10 @@
         <v>-0.1448434009083171</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9731958849554272</v>
+        <v>0.9731958849554273</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5287372056238219</v>
+        <v>0.528737205623822</v>
       </c>
       <c r="K6" t="n">
         <v>0.9895856291310562</v>
@@ -915,7 +903,7 @@
         <v>0.3500351124404424</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3576262558288169</v>
+        <v>-0.3576262558288171</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -934,16 +922,16 @@
         <v>0.9999958216713742</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2056745417783347</v>
+        <v>0.2056745417783346</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1418817656516465</v>
+        <v>-0.1418817656516466</v>
       </c>
       <c r="V6" t="n">
         <v>0.9736012301388481</v>
       </c>
       <c r="W6" t="n">
-        <v>0.528516541425454</v>
+        <v>0.5285165414254541</v>
       </c>
       <c r="X6" t="n">
         <v>0.9893824518214817</v>
@@ -956,7 +944,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
@@ -965,13 +953,13 @@
         <v>-0.317899981085866</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1695082015933334</v>
+        <v>0.1695082015933333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2123628771197048</v>
+        <v>0.2123628771197047</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2047453459706184</v>
+        <v>-0.2047453459706183</v>
       </c>
       <c r="F7" t="n">
         <v>0.2093354647684069</v>
@@ -989,7 +977,7 @@
         <v>0.271520996794032</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2436206205581372</v>
+        <v>0.2436206205581373</v>
       </c>
       <c r="L7" t="n">
         <v>-0.1916737347750353</v>
@@ -1008,7 +996,7 @@
         <v>0.221378139692735</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2008248499490449</v>
+        <v>-0.2008248499490448</v>
       </c>
       <c r="S7" t="n">
         <v>0.2099892408434847</v>
@@ -1017,7 +1005,7 @@
         <v>0.9999216554975374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2827622300626428</v>
+        <v>0.2827622300626427</v>
       </c>
       <c r="V7" t="n">
         <v>0.1717392730601128</v>
@@ -1036,7 +1024,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
@@ -1045,13 +1033,13 @@
         <v>0.3820778906126966</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5218178715827039</v>
+        <v>-0.5218178715827038</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1369084253785725</v>
       </c>
       <c r="E8" t="n">
-        <v>0.368907005219515</v>
+        <v>0.3689070052195151</v>
       </c>
       <c r="F8" t="n">
         <v>-0.1448434009083171</v>
@@ -1063,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005649501984415949</v>
+        <v>0.005649501984415946</v>
       </c>
       <c r="J8" t="n">
         <v>0.4758171229957013</v>
@@ -1072,14 +1060,14 @@
         <v>-0.170965769180117</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5302871817790752</v>
+        <v>-0.5302871817790751</v>
       </c>
       <c r="M8" t="n">
         <v>0.3120877216134196</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>0.3870015144114749</v>
+        <v>0.3870015144114748</v>
       </c>
       <c r="P8" t="n">
         <v>-0.5190776715589176</v>
@@ -1094,13 +1082,13 @@
         <v>-0.1452736968032047</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2790908764172708</v>
+        <v>0.279090876417271</v>
       </c>
       <c r="U8" t="n">
         <v>0.9999330219334991</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003354441536745887</v>
+        <v>0.003354441536745919</v>
       </c>
       <c r="W8" t="n">
         <v>0.4738745585159754</v>
@@ -1112,35 +1100,35 @@
         <v>-0.5352358545235774</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3414624050985013</v>
+        <v>0.3414624050985015</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>SHORTUN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.251050212271769</v>
+        <v>-0.2510502122717689</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008001483884778154</v>
+        <v>0.008001483884778634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4325186825946399</v>
+        <v>0.43251868259464</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09713944074218601</v>
+        <v>-0.097139440742186</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9731958849554272</v>
+        <v>0.9731958849554273</v>
       </c>
       <c r="G9" t="n">
         <v>0.1715170584497409</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005649501984415949</v>
+        <v>0.005649501984415946</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1155,14 +1143,14 @@
         <v>0.2390004994054075</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2253667484441483</v>
+        <v>-0.2253667484441485</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>-0.2591839427893097</v>
+        <v>-0.2591839427893096</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007107257036336559</v>
+        <v>0.007107257036336561</v>
       </c>
       <c r="Q9" t="n">
         <v>0.431749633292726</v>
@@ -1171,13 +1159,13 @@
         <v>-0.1010360444269618</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9726845866139469</v>
+        <v>0.9726845866139467</v>
       </c>
       <c r="T9" t="n">
         <v>0.1684269294565623</v>
       </c>
       <c r="U9" t="n">
-        <v>0.008689256589290735</v>
+        <v>0.008689256589290652</v>
       </c>
       <c r="V9" t="n">
         <v>0.9999948671383795</v>
@@ -1186,7 +1174,7 @@
         <v>0.5198338875693433</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9459487029962727</v>
+        <v>0.9459487029962729</v>
       </c>
       <c r="Y9" t="n">
         <v>0.2235829146153027</v>
@@ -1196,7 +1184,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>LONGUN</t>
         </is>
@@ -1205,16 +1193,16 @@
         <v>-0.09848815227339781</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.01681270971069045</v>
+        <v>-0.01681270971069017</v>
       </c>
       <c r="D10" t="n">
         <v>0.1897759717511375</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02672745349588758</v>
+        <v>0.0267274534958875</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5287372056238219</v>
+        <v>0.528737205623822</v>
       </c>
       <c r="G10" t="n">
         <v>0.271520996794032</v>
@@ -1229,29 +1217,29 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5508529577894344</v>
+        <v>0.5508529577894345</v>
       </c>
       <c r="L10" t="n">
         <v>-0.1346701136905838</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.188706025376279</v>
+        <v>-0.1887060253762791</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>-0.0972105982765111</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.01457472975084462</v>
+        <v>-0.0145747297508446</v>
       </c>
       <c r="Q10" t="n">
         <v>0.192498973217508</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02641754290330003</v>
+        <v>0.02641754290330002</v>
       </c>
       <c r="S10" t="n">
-        <v>0.529917766684068</v>
+        <v>0.5299177666840681</v>
       </c>
       <c r="T10" t="n">
         <v>0.2687096998598872</v>
@@ -1266,7 +1254,7 @@
         <v>0.9999608740892582</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5509988529970685</v>
+        <v>0.5509988529970686</v>
       </c>
       <c r="Y10" t="n">
         <v>-0.1429626745219034</v>
@@ -1276,16 +1264,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>LF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4227834725036978</v>
+        <v>-0.4227834725036979</v>
       </c>
       <c r="C11" t="n">
-        <v>0.258471533393825</v>
+        <v>0.2584715333938255</v>
       </c>
       <c r="D11" t="n">
         <v>0.4586087222621897</v>
@@ -1297,7 +1285,7 @@
         <v>0.9895856291310562</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2436206205581372</v>
+        <v>0.2436206205581373</v>
       </c>
       <c r="H11" t="n">
         <v>-0.170965769180117</v>
@@ -1306,7 +1294,7 @@
         <v>0.9464517064310926</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5508529577894344</v>
+        <v>0.5508529577894345</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -1315,11 +1303,11 @@
         <v>0.3808285597060046</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4222028295490291</v>
+        <v>-0.4222028295490293</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>-0.4297887500989953</v>
+        <v>-0.4297887500989954</v>
       </c>
       <c r="P11" t="n">
         <v>0.258148215748512</v>
@@ -1337,26 +1325,26 @@
         <v>0.2398137065281173</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1681023786144135</v>
+        <v>-0.1681023786144136</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9469045908684025</v>
+        <v>0.9469045908684024</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5507665035280203</v>
+        <v>0.5507665035280204</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9999985546791555</v>
+        <v>0.9999985546791554</v>
       </c>
       <c r="Y11" t="n">
         <v>0.3665530777698816</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.4436428589347686</v>
+        <v>-0.4436428589347687</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>REER</t>
         </is>
@@ -1365,13 +1353,13 @@
         <v>-0.6511442979749542</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7188545818735906</v>
+        <v>0.7188545818735909</v>
       </c>
       <c r="D12" t="n">
         <v>0.3490437715482603</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.617561074095845</v>
+        <v>-0.6175610740958448</v>
       </c>
       <c r="F12" t="n">
         <v>0.3500351124404424</v>
@@ -1380,7 +1368,7 @@
         <v>-0.1916737347750353</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5302871817790752</v>
+        <v>-0.5302871817790751</v>
       </c>
       <c r="I12" t="n">
         <v>0.2390004994054075</v>
@@ -1399,34 +1387,34 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>-0.6516723750703195</v>
+        <v>-0.6516723750703196</v>
       </c>
       <c r="P12" t="n">
-        <v>0.71850337745338</v>
+        <v>0.7185033774533801</v>
       </c>
       <c r="Q12" t="n">
         <v>0.3543569647243747</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.6205978268775474</v>
+        <v>-0.6205978268775473</v>
       </c>
       <c r="S12" t="n">
         <v>0.3507314487657855</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1925225379966611</v>
+        <v>-0.1925225379966613</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5333082110214256</v>
+        <v>-0.5333082110214257</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2398846015785885</v>
+        <v>0.2398846015785884</v>
       </c>
       <c r="W12" t="n">
         <v>-0.1357370080770097</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3814113712653678</v>
+        <v>0.3814113712653677</v>
       </c>
       <c r="Y12" t="n">
         <v>0.9997068511843753</v>
@@ -1436,25 +1424,25 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9752949454945217</v>
+        <v>0.975294945494522</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.8778495188046286</v>
+        <v>-0.8778495188046287</v>
       </c>
       <c r="D13" t="n">
         <v>-0.4980434800236231</v>
       </c>
       <c r="E13" t="n">
-        <v>0.861899747052612</v>
+        <v>0.8618997470526121</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3576262558288169</v>
+        <v>-0.3576262558288171</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4308907206412813</v>
@@ -1463,13 +1451,13 @@
         <v>0.3120877216134196</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2253667484441483</v>
+        <v>-0.2253667484441485</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.188706025376279</v>
+        <v>-0.1887060253762791</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4222028295490291</v>
+        <v>-0.4222028295490293</v>
       </c>
       <c r="L13" t="n">
         <v>-0.5748005400260326</v>
@@ -1479,44 +1467,44 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>0.9735638725976661</v>
+        <v>0.9735638725976662</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8779467071522156</v>
+        <v>-0.8779467071522152</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.5063521839868641</v>
+        <v>-0.5063521839868637</v>
       </c>
       <c r="R13" t="n">
         <v>0.8633292433241694</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3590517130525022</v>
+        <v>-0.3590517130525023</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4246333277994186</v>
+        <v>-0.4246333277994183</v>
       </c>
       <c r="U13" t="n">
         <v>0.3076414111587107</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2266663053555415</v>
+        <v>-0.2266663053555417</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1915274962701164</v>
+        <v>-0.1915274962701166</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4229755120620183</v>
+        <v>-0.4229755120620186</v>
       </c>
       <c r="Y13" t="n">
         <v>-0.572016874588974</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.9985695546139848</v>
+        <v>0.9985695546139849</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>trend</t>
         </is>
@@ -1548,13 +1536,13 @@
       <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>i_lag1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9998992510323782</v>
+        <v>0.9998992510323784</v>
       </c>
       <c r="C15" t="n">
         <v>-0.8838733630051855</v>
@@ -1563,7 +1551,7 @@
         <v>-0.5467211625965621</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8808462549912839</v>
+        <v>0.8808462549912837</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3794713412119078</v>
@@ -1572,22 +1560,22 @@
         <v>-0.3147673580817734</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3870015144114749</v>
+        <v>0.3870015144114748</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2591839427893097</v>
+        <v>-0.2591839427893096</v>
       </c>
       <c r="J15" t="n">
         <v>-0.0972105982765111</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4297887500989953</v>
+        <v>-0.4297887500989954</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6516723750703195</v>
+        <v>-0.6516723750703196</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9735638725976661</v>
+        <v>0.9735638725976662</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
@@ -1603,10 +1591,10 @@
         <v>0.8833102070746268</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3805998627277794</v>
+        <v>-0.3805998627277795</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3084057649320927</v>
+        <v>-0.3084057649320923</v>
       </c>
       <c r="U15" t="n">
         <v>0.3829351012627208</v>
@@ -1628,7 +1616,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>P_lag1</t>
         </is>
@@ -1637,13 +1625,13 @@
         <v>-0.8842654704070894</v>
       </c>
       <c r="C16" t="n">
-        <v>0.999979598161744</v>
+        <v>0.9999795981617441</v>
       </c>
       <c r="D16" t="n">
         <v>0.3776092347085051</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8851276130955023</v>
+        <v>-0.885127613095502</v>
       </c>
       <c r="F16" t="n">
         <v>0.1682692850620333</v>
@@ -1655,19 +1643,19 @@
         <v>-0.5190776715589176</v>
       </c>
       <c r="I16" t="n">
-        <v>0.007107257036336559</v>
+        <v>0.007107257036336561</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.01457472975084462</v>
+        <v>-0.0145747297508446</v>
       </c>
       <c r="K16" t="n">
         <v>0.258148215748512</v>
       </c>
       <c r="L16" t="n">
-        <v>0.71850337745338</v>
+        <v>0.7185033774533801</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8779467071522156</v>
+        <v>-0.8779467071522152</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
@@ -1677,22 +1665,22 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3884298704634139</v>
+        <v>0.3884298704634138</v>
       </c>
       <c r="R16" t="n">
         <v>-0.8852968355379425</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1700969811393862</v>
+        <v>0.1700969811393863</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1678655289746107</v>
+        <v>0.1678655289746103</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5184085312012291</v>
+        <v>-0.518408531201229</v>
       </c>
       <c r="V16" t="n">
-        <v>0.008372949068144668</v>
+        <v>0.008372949068144614</v>
       </c>
       <c r="W16" t="n">
         <v>-0.01303785105148817</v>
@@ -1701,14 +1689,14 @@
         <v>0.2592632373217938</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.721432871179901</v>
+        <v>0.7214328711799012</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.8857392591030766</v>
+        <v>-0.8857392591030769</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>W_lag1</t>
         </is>
@@ -1717,7 +1705,7 @@
         <v>-0.5494848526145703</v>
       </c>
       <c r="C17" t="n">
-        <v>0.391177043687978</v>
+        <v>0.3911770436879778</v>
       </c>
       <c r="D17" t="n">
         <v>0.9997357335696246</v>
@@ -1747,14 +1735,14 @@
         <v>0.3543569647243747</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5063521839868641</v>
+        <v>-0.5063521839868637</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>-0.5542668498278355</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3884298704634139</v>
+        <v>0.3884298704634138</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1766,7 +1754,7 @@
         <v>0.4798409053658618</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2138249347285086</v>
+        <v>0.2138249347285081</v>
       </c>
       <c r="U17" t="n">
         <v>-0.1335823715499757</v>
@@ -1784,11 +1772,11 @@
         <v>0.3439202139385749</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.5175167589563435</v>
+        <v>-0.5175167589563436</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>WR_lag1</t>
         </is>
@@ -1797,7 +1785,7 @@
         <v>0.8831287957144771</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.8857251257792353</v>
+        <v>-0.8857251257792357</v>
       </c>
       <c r="D18" t="n">
         <v>-0.3552736332744265</v>
@@ -1809,7 +1797,7 @@
         <v>-0.1938391280326576</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2008248499490449</v>
+        <v>-0.2008248499490448</v>
       </c>
       <c r="H18" t="n">
         <v>0.3714634965822222</v>
@@ -1818,13 +1806,13 @@
         <v>-0.1010360444269618</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02641754290330003</v>
+        <v>0.02641754290330002</v>
       </c>
       <c r="K18" t="n">
         <v>-0.2574446893035903</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6205978268775474</v>
+        <v>-0.6205978268775473</v>
       </c>
       <c r="M18" t="n">
         <v>0.8633292433241694</v>
@@ -1846,16 +1834,16 @@
         <v>-0.1948545670304899</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1950071619437683</v>
+        <v>-0.195007161943768</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3686958315453534</v>
+        <v>0.3686958315453533</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1021371735328213</v>
       </c>
       <c r="W18" t="n">
-        <v>0.02343680113825215</v>
+        <v>0.02343680113825209</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2580362430679972</v>
@@ -1868,7 +1856,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>GDP_lag1</t>
         </is>
@@ -1877,13 +1865,13 @@
         <v>-0.3732451966537225</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1707307134684574</v>
+        <v>0.1707307134684579</v>
       </c>
       <c r="D19" t="n">
         <v>0.4786708181867887</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1909683191999004</v>
+        <v>-0.1909683191999005</v>
       </c>
       <c r="F19" t="n">
         <v>0.9999958216713742</v>
@@ -1895,10 +1883,10 @@
         <v>-0.1452736968032047</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9726845866139469</v>
+        <v>0.9726845866139467</v>
       </c>
       <c r="J19" t="n">
-        <v>0.529917766684068</v>
+        <v>0.5299177666840681</v>
       </c>
       <c r="K19" t="n">
         <v>0.9898984782129713</v>
@@ -1907,14 +1895,14 @@
         <v>0.3507314487657855</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3590517130525022</v>
+        <v>-0.3590517130525023</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>-0.3805998627277794</v>
+        <v>-0.3805998627277795</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1700969811393862</v>
+        <v>0.1700969811393863</v>
       </c>
       <c r="Q19" t="n">
         <v>0.4798409053658618</v>
@@ -1926,16 +1914,16 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2063242456939633</v>
+        <v>0.2063242456939632</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1423177820398876</v>
+        <v>-0.1423177820398877</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9730908600513728</v>
+        <v>0.9730908600513729</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5296972007725277</v>
+        <v>0.5296972007725278</v>
       </c>
       <c r="X19" t="n">
         <v>0.9896996058635071</v>
@@ -1948,31 +1936,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>LS_lag1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3115988637288141</v>
+        <v>-0.3115988637288138</v>
       </c>
       <c r="C20" t="n">
-        <v>0.16488269473364</v>
+        <v>0.1648826947336396</v>
       </c>
       <c r="D20" t="n">
-        <v>0.20475216561385</v>
+        <v>0.2047521656138495</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1990443653837984</v>
+        <v>-0.1990443653837979</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2056745417783347</v>
+        <v>0.2056745417783346</v>
       </c>
       <c r="G20" t="n">
         <v>0.9999216554975374</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2790908764172708</v>
+        <v>0.279090876417271</v>
       </c>
       <c r="I20" t="n">
         <v>0.1684269294565623</v>
@@ -1984,87 +1972,87 @@
         <v>0.2398137065281173</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1925225379966611</v>
+        <v>-0.1925225379966613</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4246333277994186</v>
+        <v>-0.4246333277994183</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>-0.3084057649320927</v>
+        <v>-0.3084057649320923</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1678655289746107</v>
+        <v>0.1678655289746103</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2138249347285086</v>
+        <v>0.2138249347285081</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.1950071619437683</v>
+        <v>-0.195007161943768</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2063242456939633</v>
+        <v>0.2063242456939632</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.285778548497009</v>
+        <v>0.2857785484970094</v>
       </c>
       <c r="V20" t="n">
         <v>0.168635491090332</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2692572116296649</v>
+        <v>0.2692572116296651</v>
       </c>
       <c r="X20" t="n">
         <v>0.2400953600345279</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.2078970793865168</v>
+        <v>-0.2078970793865171</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.3996771231579779</v>
+        <v>-0.3996771231579778</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>UN_lag1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3780556684554928</v>
+        <v>0.3780556684554927</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.5211286847283035</v>
+        <v>-0.5211286847283034</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1327089361697054</v>
+        <v>-0.1327089361697055</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3661557605034371</v>
+        <v>0.366155760503437</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1418817656516465</v>
+        <v>-0.1418817656516466</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2827622300626428</v>
+        <v>0.2827622300626427</v>
       </c>
       <c r="H21" t="n">
         <v>0.9999330219334991</v>
       </c>
       <c r="I21" t="n">
-        <v>0.008689256589290735</v>
+        <v>0.008689256589290652</v>
       </c>
       <c r="J21" t="n">
         <v>0.4762839524202594</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1681023786144135</v>
+        <v>-0.1681023786144136</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5333082110214256</v>
+        <v>-0.5333082110214257</v>
       </c>
       <c r="M21" t="n">
         <v>0.3076414111587107</v>
@@ -2074,25 +2062,25 @@
         <v>0.3829351012627208</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5184085312012291</v>
+        <v>-0.518408531201229</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.1335823715499757</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3686958315453534</v>
+        <v>0.3686958315453533</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1423177820398876</v>
+        <v>-0.1423177820398877</v>
       </c>
       <c r="T21" t="n">
-        <v>0.285778548497009</v>
+        <v>0.2857785484970094</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.006413457049977922</v>
+        <v>0.006413457049977855</v>
       </c>
       <c r="W21" t="n">
         <v>0.474406650511995</v>
@@ -2101,14 +2089,14 @@
         <v>-0.1686426088107265</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.5383523291728965</v>
+        <v>-0.5383523291728967</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.3370212832173737</v>
+        <v>0.3370212832173738</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>SHORTUN_lag1</t>
         </is>
@@ -2117,7 +2105,7 @@
         <v>-0.2523627093172098</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00927383905652389</v>
+        <v>0.009273839056524381</v>
       </c>
       <c r="D22" t="n">
         <v>0.4329105172837279</v>
@@ -2132,7 +2120,7 @@
         <v>0.1717392730601128</v>
       </c>
       <c r="H22" t="n">
-        <v>0.003354441536745887</v>
+        <v>0.003354441536745919</v>
       </c>
       <c r="I22" t="n">
         <v>0.9999948671383795</v>
@@ -2141,20 +2129,20 @@
         <v>0.5192318074927588</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9469045908684025</v>
+        <v>0.9469045908684024</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2398846015785885</v>
+        <v>0.2398846015785884</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2266663053555415</v>
+        <v>-0.2266663053555417</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
         <v>-0.2605037705405707</v>
       </c>
       <c r="P22" t="n">
-        <v>0.008372949068144668</v>
+        <v>0.008372949068144614</v>
       </c>
       <c r="Q22" t="n">
         <v>0.4321440448715353</v>
@@ -2163,13 +2151,13 @@
         <v>-0.1021371735328213</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9730908600513728</v>
+        <v>0.9730908600513729</v>
       </c>
       <c r="T22" t="n">
         <v>0.168635491090332</v>
       </c>
       <c r="U22" t="n">
-        <v>0.006413457049977922</v>
+        <v>0.006413457049977855</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
@@ -2188,7 +2176,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>LONGUN_lag1</t>
         </is>
@@ -2197,16 +2185,16 @@
         <v>-0.1010793827831545</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0152591156095372</v>
+        <v>-0.01525911560953693</v>
       </c>
       <c r="D23" t="n">
         <v>0.1891807162780484</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02373977285307798</v>
+        <v>0.0237397728530779</v>
       </c>
       <c r="F23" t="n">
-        <v>0.528516541425454</v>
+        <v>0.5285165414254541</v>
       </c>
       <c r="G23" t="n">
         <v>0.2721270808902367</v>
@@ -2221,13 +2209,13 @@
         <v>0.9999608740892582</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5507665035280203</v>
+        <v>0.5507665035280204</v>
       </c>
       <c r="L23" t="n">
         <v>-0.1357370080770097</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1915274962701164</v>
+        <v>-0.1915274962701166</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2240,13 +2228,13 @@
         <v>0.1918781502696367</v>
       </c>
       <c r="R23" t="n">
-        <v>0.02343680113825215</v>
+        <v>0.02343680113825209</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5296972007725277</v>
+        <v>0.5296972007725278</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2692572116296649</v>
+        <v>0.2692572116296651</v>
       </c>
       <c r="U23" t="n">
         <v>0.474406650511995</v>
@@ -2258,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.5509110539209439</v>
+        <v>0.550911053920944</v>
       </c>
       <c r="Y23" t="n">
         <v>-0.1439840961276608</v>
@@ -2268,7 +2256,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>LF_lag1</t>
         </is>
@@ -2277,7 +2265,7 @@
         <v>-0.423364096374065</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2595819444228162</v>
+        <v>0.2595819444228167</v>
       </c>
       <c r="D24" t="n">
         <v>0.4584864031081042</v>
@@ -2295,19 +2283,19 @@
         <v>-0.1715008516431696</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9459487029962727</v>
+        <v>0.9459487029962729</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5509988529970685</v>
+        <v>0.5509988529970686</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9999985546791555</v>
+        <v>0.9999985546791554</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3814113712653678</v>
+        <v>0.3814113712653677</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4229755120620183</v>
+        <v>-0.4229755120620186</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -2335,7 +2323,7 @@
         <v>0.9464025193226209</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5509110539209439</v>
+        <v>0.550911053920944</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -2348,7 +2336,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>REER_lag1</t>
         </is>
@@ -2357,7 +2345,7 @@
         <v>-0.6488783302109221</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7218128932997563</v>
+        <v>0.7218128932997564</v>
       </c>
       <c r="D25" t="n">
         <v>0.3386512962748404</v>
@@ -2394,7 +2382,7 @@
         <v>-0.6493463916935112</v>
       </c>
       <c r="P25" t="n">
-        <v>0.721432871179901</v>
+        <v>0.7214328711799012</v>
       </c>
       <c r="Q25" t="n">
         <v>0.3439202139385749</v>
@@ -2406,10 +2394,10 @@
         <v>0.3355235845597406</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2078970793865168</v>
+        <v>-0.2078970793865171</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5383523291728965</v>
+        <v>-0.5383523291728967</v>
       </c>
       <c r="V25" t="n">
         <v>0.2244678956379136</v>
@@ -2424,23 +2412,23 @@
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.5914732685240417</v>
+        <v>-0.5914732685240418</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>SH_lag1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9812990370124334</v>
+        <v>0.9812990370124332</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.8858558550615289</v>
+        <v>-0.8858558550615293</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5090969913149572</v>
+        <v>-0.5090969913149573</v>
       </c>
       <c r="E26" t="n">
         <v>0.8693091337618186</v>
@@ -2452,7 +2440,7 @@
         <v>-0.4061031444713954</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3414624050985013</v>
+        <v>0.3414624050985015</v>
       </c>
       <c r="I26" t="n">
         <v>-0.247093399352565</v>
@@ -2461,23 +2449,23 @@
         <v>-0.1757992546415682</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4436428589347686</v>
+        <v>-0.4436428589347687</v>
       </c>
       <c r="L26" t="n">
         <v>-0.5941183133398302</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9985695546139848</v>
+        <v>0.9985695546139849</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
         <v>0.9802254902179603</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.8857392591030766</v>
+        <v>-0.8857392591030769</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.5175167589563435</v>
+        <v>-0.5175167589563436</v>
       </c>
       <c r="R26" t="n">
         <v>0.8708958033182209</v>
@@ -2486,10 +2474,10 @@
         <v>-0.3800350874118151</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3996771231579779</v>
+        <v>-0.3996771231579778</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3370212832173737</v>
+        <v>0.3370212832173738</v>
       </c>
       <c r="V26" t="n">
         <v>-0.248428669346725</v>
@@ -2501,7 +2489,7 @@
         <v>-0.4443986261311992</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.5914732685240417</v>
+        <v>-0.5914732685240418</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
